--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B5EA0E-6D2B-4274-A181-379D98C898EE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BBD46AC-CBBC-4C5A-B16B-B5E01CDDDCC2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="48">
   <si>
     <t>Josue</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>Semana del 14 al 18  Septiembre</t>
+  </si>
+  <si>
+    <t>Semana del 21 al 25 Septiembre</t>
   </si>
 </sst>
 </file>
@@ -335,10 +338,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -681,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B5EDDC-5ADB-4A4C-9736-3AC62D35C32F}">
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="18.8984375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="19.59765625" bestFit="1" customWidth="1"/>
@@ -705,27 +708,27 @@
       <c r="A1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="11"/>
+      <c r="B1" s="10"/>
       <c r="D1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="11"/>
+      <c r="E1" s="10"/>
       <c r="G1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="11"/>
+      <c r="H1" s="10"/>
       <c r="J1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="11"/>
+      <c r="K1" s="10"/>
       <c r="M1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="11"/>
+      <c r="N1" s="10"/>
       <c r="P1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="11"/>
+      <c r="Q1" s="10"/>
     </row>
     <row r="2" spans="1:17" ht="15.6" customHeight="1">
       <c r="A2" s="4" t="s">
@@ -1095,23 +1098,23 @@
       <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="11"/>
+      <c r="B14" s="10"/>
       <c r="D14" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="11"/>
+      <c r="E14" s="10"/>
       <c r="G14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="11"/>
+      <c r="H14" s="10"/>
       <c r="J14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="K14" s="11"/>
+      <c r="K14" s="10"/>
       <c r="M14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="N14" s="11"/>
+      <c r="N14" s="10"/>
     </row>
     <row r="15" spans="1:17" ht="15.6">
       <c r="A15" s="4" t="s">
@@ -1400,26 +1403,26 @@
       </c>
     </row>
     <row r="28" spans="1:14" ht="15.6">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="10"/>
-      <c r="D28" s="10" t="s">
+      <c r="B28" s="11"/>
+      <c r="D28" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="10"/>
-      <c r="G28" s="10" t="s">
+      <c r="E28" s="11"/>
+      <c r="G28" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="10"/>
+      <c r="H28" s="11"/>
       <c r="J28" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="K28" s="10"/>
+      <c r="K28" s="11"/>
       <c r="M28" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="N28" s="10"/>
+      <c r="N28" s="11"/>
     </row>
     <row r="29" spans="1:14" ht="15.6">
       <c r="A29" s="7" t="s">
@@ -1549,19 +1552,19 @@
       <c r="A36" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="10"/>
+      <c r="B36" s="11"/>
       <c r="D36" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E36" s="10"/>
+      <c r="E36" s="11"/>
       <c r="G36" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H36" s="11"/>
+      <c r="H36" s="10"/>
       <c r="J36" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="K36" s="11"/>
+      <c r="K36" s="10"/>
       <c r="M36" s="12" t="s">
         <v>46</v>
       </c>
@@ -1679,8 +1682,57 @@
         <v>11</v>
       </c>
     </row>
+    <row r="42" spans="1:14" ht="15.6" customHeight="1">
+      <c r="A42" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="10"/>
+    </row>
+    <row r="43" spans="1:14" ht="15.6">
+      <c r="A43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="15.6">
+      <c r="A44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="15.6">
+      <c r="A45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="15.6">
+      <c r="A46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="M36:N36"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="D14:E14"/>
@@ -1692,16 +1744,6 @@
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="J14:K14"/>
     <mergeCell ref="M14:N14"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="M36:N36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BBD46AC-CBBC-4C5A-B16B-B5E01CDDDCC2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297B7825-75E9-46BF-AE25-2C5E09D0C442}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
+    <workbookView xWindow="-28920" yWindow="2475" windowWidth="29040" windowHeight="15720" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Teletrabajo" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="49">
   <si>
     <t>Josue</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>Semana del 21 al 25 Septiembre</t>
+  </si>
+  <si>
+    <t>Semana del 28 Septiembre al 2 de Octubre</t>
   </si>
 </sst>
 </file>
@@ -1687,6 +1690,10 @@
         <v>47</v>
       </c>
       <c r="B42" s="10"/>
+      <c r="D42" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E42" s="10"/>
     </row>
     <row r="43" spans="1:14" ht="15.6">
       <c r="A43" s="1" t="s">
@@ -1695,6 +1702,12 @@
       <c r="B43" s="8" t="s">
         <v>1</v>
       </c>
+      <c r="D43" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="44" spans="1:14" ht="15.6">
       <c r="A44" s="1" t="s">
@@ -1703,6 +1716,12 @@
       <c r="B44" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="D44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="45" spans="1:14" ht="15.6">
       <c r="A45" s="1" t="s">
@@ -1710,6 +1729,12 @@
       </c>
       <c r="B45" s="8" t="s">
         <v>6</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="15.6">
@@ -1719,9 +1744,26 @@
       <c r="B46" s="8" t="s">
         <v>8</v>
       </c>
+      <c r="D46" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="M14:N14"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="D36:E36"/>
@@ -1733,17 +1775,7 @@
     <mergeCell ref="G36:H36"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="M36:N36"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="D42:E42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297B7825-75E9-46BF-AE25-2C5E09D0C442}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D62BF1-1B6F-4182-A367-A5611B09DC7A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2475" windowWidth="29040" windowHeight="15720" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Teletrabajo" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="50">
   <si>
     <t>Josue</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>Semana del 28 Septiembre al 2 de Octubre</t>
+  </si>
+  <si>
+    <t>Semana 05 al 09 de Octubre</t>
   </si>
 </sst>
 </file>
@@ -258,7 +261,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -316,11 +319,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -352,6 +368,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1694,6 +1713,10 @@
         <v>48</v>
       </c>
       <c r="E42" s="10"/>
+      <c r="G42" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H42" s="14"/>
     </row>
     <row r="43" spans="1:14" ht="15.6">
       <c r="A43" s="1" t="s">
@@ -1708,6 +1731,12 @@
       <c r="E43" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="G43" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:14" ht="15.6">
       <c r="A44" s="1" t="s">
@@ -1722,6 +1751,12 @@
       <c r="E44" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="G44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="45" spans="1:14" ht="15.6">
       <c r="A45" s="1" t="s">
@@ -1735,6 +1770,12 @@
       </c>
       <c r="E45" s="2" t="s">
         <v>8</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="15.6">
@@ -1750,20 +1791,15 @@
       <c r="E46" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="G46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="M14:N14"/>
+  <mergeCells count="24">
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="D36:E36"/>
@@ -1776,6 +1812,18 @@
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="M36:N36"/>
     <mergeCell ref="D42:E42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="M14:N14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D62BF1-1B6F-4182-A367-A5611B09DC7A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D80D53-1CA8-46D4-9FA8-692407C49C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="51">
   <si>
     <t>Josue</t>
   </si>
@@ -186,13 +186,16 @@
   </si>
   <si>
     <t>Semana 05 al 09 de Octubre</t>
+  </si>
+  <si>
+    <t>Semana 12 al 16 de Octubre</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,7 +339,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -370,6 +373,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -707,26 +713,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B5EDDC-5ADB-4A4C-9736-3AC62D35C32F}">
   <dimension ref="A1:Q46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="18.8984375" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.3984375" customWidth="1"/>
-    <col min="4" max="4" width="18.69921875" customWidth="1"/>
-    <col min="5" max="5" width="12.296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.8984375" customWidth="1"/>
-    <col min="7" max="7" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.59765625" customWidth="1"/>
-    <col min="11" max="11" width="12.296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3.8984375" customWidth="1"/>
-    <col min="14" max="14" width="12.296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.69921875" customWidth="1"/>
-    <col min="17" max="17" width="12.296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.69921875" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.88671875" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.88671875" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.6640625" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6" customHeight="1">
+    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>18</v>
       </c>
@@ -752,7 +758,7 @@
       </c>
       <c r="Q1" s="10"/>
     </row>
-    <row r="2" spans="1:17" ht="15.6" customHeight="1">
+    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
@@ -790,7 +796,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.6">
+    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -828,7 +834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.6">
+    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -866,7 +872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.6">
+    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -904,7 +910,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.6">
+    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -942,7 +948,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.6">
+    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -980,7 +986,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.6">
+    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -1018,7 +1024,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.6">
+    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1050,7 +1056,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.6">
+    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="G10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1076,7 +1082,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.6">
+    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J11" s="1" t="s">
         <v>13</v>
       </c>
@@ -1096,7 +1102,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.6">
+    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1116,7 +1122,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.6">
+    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
@@ -1138,7 +1144,7 @@
       </c>
       <c r="N14" s="10"/>
     </row>
-    <row r="15" spans="1:17" ht="15.6">
+    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
@@ -1170,7 +1176,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.6">
+    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -1202,7 +1208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="15.6">
+    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1234,7 +1240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15.6">
+    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1266,7 +1272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15.6">
+    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1298,7 +1304,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15.6">
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -1330,7 +1336,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15.6">
+    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
@@ -1362,7 +1368,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15.6">
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
@@ -1388,7 +1394,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="15.6">
+    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1408,7 +1414,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="15.6">
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1416,7 +1422,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="15.6">
+    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>2</v>
       </c>
@@ -1424,7 +1430,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="15.6">
+    <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>34</v>
       </c>
@@ -1446,7 +1452,7 @@
       </c>
       <c r="N28" s="11"/>
     </row>
-    <row r="29" spans="1:14" ht="15.6">
+    <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>5</v>
       </c>
@@ -1478,7 +1484,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15.6">
+    <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>3</v>
       </c>
@@ -1510,7 +1516,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15.6">
+    <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>13</v>
       </c>
@@ -1542,7 +1548,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15.6">
+    <row r="32" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>16</v>
       </c>
@@ -1556,7 +1562,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="15.6">
+    <row r="33" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>2</v>
       </c>
@@ -1566,11 +1572,11 @@
       <c r="G33" s="1"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:14" ht="15.6">
+    <row r="34" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="G34" s="1"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="36" spans="1:14" ht="31.5" customHeight="1">
+    <row r="36" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>42</v>
       </c>
@@ -1592,7 +1598,7 @@
       </c>
       <c r="N36" s="13"/>
     </row>
-    <row r="37" spans="1:14" ht="15.6">
+    <row r="37" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>2</v>
       </c>
@@ -1624,7 +1630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="15.6">
+    <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>15</v>
       </c>
@@ -1656,7 +1662,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="15.6">
+    <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="2"/>
       <c r="D39" s="1" t="s">
@@ -1684,7 +1690,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="15.6">
+    <row r="40" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D40" s="1" t="s">
         <v>0</v>
       </c>
@@ -1704,7 +1710,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="15.6" customHeight="1">
+    <row r="42" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
         <v>47</v>
       </c>
@@ -1717,8 +1723,12 @@
         <v>49</v>
       </c>
       <c r="H42" s="14"/>
-    </row>
-    <row r="43" spans="1:14" ht="15.6">
+      <c r="J42" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K42" s="15"/>
+    </row>
+    <row r="43" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>13</v>
       </c>
@@ -1737,8 +1747,14 @@
       <c r="H43" s="8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" ht="15.6">
+      <c r="J43" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>2</v>
       </c>
@@ -1757,8 +1773,14 @@
       <c r="H44" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" ht="15.6">
+      <c r="J44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>3</v>
       </c>
@@ -1777,8 +1799,14 @@
       <c r="H45" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" ht="15.6">
+      <c r="J45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>14</v>
       </c>
@@ -1799,7 +1827,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="D36:E36"/>
@@ -1813,6 +1841,7 @@
     <mergeCell ref="M36:N36"/>
     <mergeCell ref="D42:E42"/>
     <mergeCell ref="G42:H42"/>
+    <mergeCell ref="J42:K42"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="D14:E14"/>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D80D53-1CA8-46D4-9FA8-692407C49C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{26D80D53-1CA8-46D4-9FA8-692407C49C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C36AFA34-7527-4C82-8019-CA0140FF1E5E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="52">
   <si>
     <t>Josue</t>
   </si>
@@ -189,6 +189,9 @@
   </si>
   <si>
     <t>Semana 12 al 16 de Octubre</t>
+  </si>
+  <si>
+    <t>Semana 19 al 23 de Octubre</t>
   </si>
 </sst>
 </file>
@@ -339,7 +342,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -377,6 +380,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1727,6 +1733,10 @@
         <v>50</v>
       </c>
       <c r="K42" s="15"/>
+      <c r="M42" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="15"/>
     </row>
     <row r="43" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
@@ -1753,6 +1763,12 @@
       <c r="K43" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="M43" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
@@ -1779,6 +1795,12 @@
       <c r="K44" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="M44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="45" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
@@ -1804,6 +1826,12 @@
       </c>
       <c r="K45" s="2" t="s">
         <v>8</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
@@ -1825,9 +1853,26 @@
       <c r="H46" s="8" t="s">
         <v>8</v>
       </c>
+      <c r="M46" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="M14:N14"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="D36:E36"/>
@@ -1842,17 +1887,7 @@
     <mergeCell ref="D42:E42"/>
     <mergeCell ref="G42:H42"/>
     <mergeCell ref="J42:K42"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M42:N42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{26D80D53-1CA8-46D4-9FA8-692407C49C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C36AFA34-7527-4C82-8019-CA0140FF1E5E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DEEFD56-6D65-40B1-8050-0CD4D26121C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="53">
   <si>
     <t>Josue</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>Semana 19 al 23 de Octubre</t>
+  </si>
+  <si>
+    <t>Semana 26 al 30 de Octubre</t>
   </si>
 </sst>
 </file>
@@ -360,6 +363,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -380,9 +386,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -718,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B5EDDC-5ADB-4A4C-9736-3AC62D35C32F}">
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="18.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
@@ -739,30 +742,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="D1" s="9" t="s">
+      <c r="B1" s="11"/>
+      <c r="D1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="G1" s="9" t="s">
+      <c r="E1" s="11"/>
+      <c r="G1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="10"/>
-      <c r="J1" s="9" t="s">
+      <c r="H1" s="11"/>
+      <c r="J1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="10"/>
-      <c r="M1" s="9" t="s">
+      <c r="K1" s="11"/>
+      <c r="M1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="10"/>
-      <c r="P1" s="9" t="s">
+      <c r="N1" s="11"/>
+      <c r="P1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="10"/>
+      <c r="Q1" s="11"/>
     </row>
     <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
@@ -1129,26 +1132,26 @@
       </c>
     </row>
     <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="D14" s="9" t="s">
+      <c r="B14" s="11"/>
+      <c r="D14" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="10"/>
-      <c r="G14" s="9" t="s">
+      <c r="E14" s="11"/>
+      <c r="G14" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="10"/>
-      <c r="J14" s="9" t="s">
+      <c r="H14" s="11"/>
+      <c r="J14" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="K14" s="10"/>
-      <c r="M14" s="9" t="s">
+      <c r="K14" s="11"/>
+      <c r="M14" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="N14" s="10"/>
+      <c r="N14" s="11"/>
     </row>
     <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
@@ -1437,26 +1440,26 @@
       </c>
     </row>
     <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="11"/>
-      <c r="D28" s="11" t="s">
+      <c r="B28" s="12"/>
+      <c r="D28" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="11"/>
-      <c r="G28" s="11" t="s">
+      <c r="E28" s="12"/>
+      <c r="G28" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="11"/>
-      <c r="J28" s="9" t="s">
+      <c r="H28" s="12"/>
+      <c r="J28" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="K28" s="11"/>
-      <c r="M28" s="9" t="s">
+      <c r="K28" s="12"/>
+      <c r="M28" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="N28" s="11"/>
+      <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
@@ -1583,26 +1586,26 @@
       <c r="H34" s="2"/>
     </row>
     <row r="36" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="11"/>
-      <c r="D36" s="9" t="s">
+      <c r="B36" s="12"/>
+      <c r="D36" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E36" s="11"/>
-      <c r="G36" s="9" t="s">
+      <c r="E36" s="12"/>
+      <c r="G36" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="H36" s="10"/>
-      <c r="J36" s="9" t="s">
+      <c r="H36" s="11"/>
+      <c r="J36" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="K36" s="10"/>
-      <c r="M36" s="12" t="s">
+      <c r="K36" s="11"/>
+      <c r="M36" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N36" s="13"/>
+      <c r="N36" s="14"/>
     </row>
     <row r="37" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
@@ -1717,26 +1720,26 @@
       </c>
     </row>
     <row r="42" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B42" s="10"/>
-      <c r="D42" s="9" t="s">
+      <c r="B42" s="11"/>
+      <c r="D42" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E42" s="10"/>
-      <c r="G42" s="9" t="s">
+      <c r="E42" s="11"/>
+      <c r="G42" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H42" s="14"/>
-      <c r="J42" s="15" t="s">
+      <c r="H42" s="15"/>
+      <c r="J42" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="K42" s="15"/>
-      <c r="M42" s="15" t="s">
+      <c r="K42" s="16"/>
+      <c r="M42" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N42" s="15"/>
+      <c r="N42" s="16"/>
     </row>
     <row r="43" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
@@ -1763,7 +1766,7 @@
       <c r="K43" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="16" t="s">
+      <c r="M43" s="9" t="s">
         <v>15</v>
       </c>
       <c r="N43" s="2" t="s">
@@ -1853,26 +1856,54 @@
       <c r="H46" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="M46" s="16" t="s">
+      <c r="M46" s="9" t="s">
         <v>5</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="48" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="15"/>
+    </row>
+    <row r="49" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="M14:N14"/>
+  <mergeCells count="27">
+    <mergeCell ref="A48:B48"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="D36:E36"/>
@@ -1888,6 +1919,17 @@
     <mergeCell ref="G42:H42"/>
     <mergeCell ref="J42:K42"/>
     <mergeCell ref="M42:N42"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="M14:N14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\Subir a GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DEEFD56-6D65-40B1-8050-0CD4D26121C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41D6295-D26A-4E77-A0BC-1868C4FA8C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Teletrabajo" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="55">
   <si>
     <t>Josue</t>
   </si>
@@ -195,6 +195,12 @@
   </si>
   <si>
     <t>Semana 26 al 30 de Octubre</t>
+  </si>
+  <si>
+    <t>Semana 2 al 6 de Noviembre</t>
+  </si>
+  <si>
+    <t>Miércoles</t>
   </si>
 </sst>
 </file>
@@ -369,6 +375,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -380,9 +389,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -722,52 +728,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B5EDDC-5ADB-4A4C-9736-3AC62D35C32F}">
   <dimension ref="A1:Q52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="18.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.88671875" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5546875" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3.88671875" customWidth="1"/>
-    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.6640625" customWidth="1"/>
-    <col min="17" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.6640625" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5703125" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.85546875" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.7109375" customWidth="1"/>
+    <col min="17" max="17" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="11"/>
+      <c r="B1" s="12"/>
       <c r="D1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="11"/>
+      <c r="E1" s="12"/>
       <c r="G1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="11"/>
+      <c r="H1" s="12"/>
       <c r="J1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="11"/>
+      <c r="K1" s="12"/>
       <c r="M1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="11"/>
+      <c r="N1" s="12"/>
       <c r="P1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="11"/>
-    </row>
-    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q1" s="12"/>
+    </row>
+    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
@@ -805,7 +811,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -843,7 +849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -881,7 +887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -919,7 +925,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -957,7 +963,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -995,7 +1001,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -1033,7 +1039,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1065,7 +1071,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="G10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1091,7 +1097,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="J11" s="1" t="s">
         <v>13</v>
       </c>
@@ -1111,7 +1117,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="J12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1131,29 +1137,29 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="11"/>
+      <c r="B14" s="12"/>
       <c r="D14" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="11"/>
+      <c r="E14" s="12"/>
       <c r="G14" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="11"/>
+      <c r="H14" s="12"/>
       <c r="J14" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="K14" s="11"/>
+      <c r="K14" s="12"/>
       <c r="M14" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="N14" s="11"/>
-    </row>
-    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="N14" s="12"/>
+    </row>
+    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
@@ -1185,7 +1191,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -1217,7 +1223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1249,7 +1255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1281,7 +1287,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1313,7 +1319,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -1345,7 +1351,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
@@ -1377,7 +1383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
@@ -1403,7 +1409,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1423,7 +1429,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1431,7 +1437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>2</v>
       </c>
@@ -1439,29 +1445,29 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
+    <row r="28" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="D28" s="12" t="s">
+      <c r="B28" s="13"/>
+      <c r="D28" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="12"/>
-      <c r="G28" s="12" t="s">
+      <c r="E28" s="13"/>
+      <c r="G28" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="12"/>
+      <c r="H28" s="13"/>
       <c r="J28" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="K28" s="12"/>
+      <c r="K28" s="13"/>
       <c r="M28" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="N28" s="12"/>
-    </row>
-    <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="N28" s="13"/>
+    </row>
+    <row r="29" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>5</v>
       </c>
@@ -1493,7 +1499,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>3</v>
       </c>
@@ -1525,7 +1531,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>13</v>
       </c>
@@ -1557,7 +1563,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>16</v>
       </c>
@@ -1571,7 +1577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>2</v>
       </c>
@@ -1581,33 +1587,33 @@
       <c r="G33" s="1"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="G34" s="1"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="36" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="12"/>
+      <c r="B36" s="13"/>
       <c r="D36" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E36" s="12"/>
+      <c r="E36" s="13"/>
       <c r="G36" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="H36" s="11"/>
+      <c r="H36" s="12"/>
       <c r="J36" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="K36" s="11"/>
-      <c r="M36" s="13" t="s">
+      <c r="K36" s="12"/>
+      <c r="M36" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="N36" s="14"/>
-    </row>
-    <row r="37" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="N36" s="15"/>
+    </row>
+    <row r="37" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>2</v>
       </c>
@@ -1639,7 +1645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>15</v>
       </c>
@@ -1671,7 +1677,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="2"/>
       <c r="D39" s="1" t="s">
@@ -1699,7 +1705,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D40" s="1" t="s">
         <v>0</v>
       </c>
@@ -1719,19 +1725,19 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B42" s="11"/>
+      <c r="B42" s="12"/>
       <c r="D42" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E42" s="11"/>
+      <c r="E42" s="12"/>
       <c r="G42" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H42" s="15"/>
+      <c r="H42" s="11"/>
       <c r="J42" s="16" t="s">
         <v>50</v>
       </c>
@@ -1741,7 +1747,7 @@
       </c>
       <c r="N42" s="16"/>
     </row>
-    <row r="43" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>13</v>
       </c>
@@ -1773,7 +1779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>2</v>
       </c>
@@ -1805,7 +1811,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>3</v>
       </c>
@@ -1837,7 +1843,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>14</v>
       </c>
@@ -1863,46 +1869,86 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="15"/>
-    </row>
-    <row r="49" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B48" s="11"/>
+      <c r="D48" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E48" s="11"/>
+    </row>
+    <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D49" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D50" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D51" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="D52" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="M14:N14"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="J28:K28"/>
@@ -1919,17 +1965,6 @@
     <mergeCell ref="G42:H42"/>
     <mergeCell ref="J42:K42"/>
     <mergeCell ref="M42:N42"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="M14:N14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
